--- a/data/trans_dic/KIDM_C_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_1_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con muchos o muchísimos problemas para dormir (autopercepción menor)</t>
+          <t>Menores con muchos o muchísimos problemas para dormir (autopercepción menor) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,09</t>
+          <t>0,33; 5,54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,01</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 22,58</t>
+          <t>2,19; 21,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,14</t>
+          <t>1,59; 13,83</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,22</t>
+          <t>0,0; 41,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,24</t>
+          <t>0,0; 36,85</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,43</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>0,0; 20,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,66</t>
+          <t>1,75; 16,58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,11</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 14,87</t>
+          <t>0,92; 12,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,25</t>
+          <t>1,15; 9,98</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 20,19</t>
+          <t>4,69; 19,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,18</t>
+          <t>2,22; 12,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,84</t>
+          <t>4,28; 13,26</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,84</t>
+          <t>2,7; 8,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,88</t>
+          <t>2,47; 7,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,91</t>
+          <t>3,06; 6,73</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con muchos o muchísimos problemas para dormir (autopercepción menor) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>390; 6631</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2639</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2475</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>558; 5383</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>738; 6402</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8253</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3181</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>607; 5749</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2142</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3433</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>424; 5940</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>844; 7330</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>11206</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2978; 12543</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1807; 10019</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6192; 19210</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>11046</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11576</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>22622</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>5677; 18714</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6712; 20753</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14774; 32497</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_1_R-Provincia-trans_dic.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,54</t>
+          <t>0,09; 5,88</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,86</t>
+          <t>0,0; 15,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 21,18</t>
+          <t>0,0; 20,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,83</t>
+          <t>1,63; 14,67</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,44</t>
+          <t>0,0; 42,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,85</t>
+          <t>0,0; 35,59</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,49</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,58</t>
+          <t>1,6; 14,02</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 13,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 12,87</t>
+          <t>0,98; 14,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,98</t>
+          <t>1,17; 9,12</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 19,75</t>
+          <t>4,58; 20,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,32</t>
+          <t>2,15; 12,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,26</t>
+          <t>4,4; 13,12</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,89</t>
+          <t>2,93; 8,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,63</t>
+          <t>2,32; 7,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,73</t>
+          <t>3,03; 6,88</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6139</t>
+          <t>0; 6628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>390; 6631</t>
+          <t>112; 7037</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2475</t>
+          <t>0; 3193</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>558; 5383</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>738; 6402</t>
+          <t>754; 6788</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8184</t>
+          <t>0; 8421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8253</t>
+          <t>0; 7973</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 3265</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4095</t>
+          <t>0; 3603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>607; 5749</t>
+          <t>555; 4862</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>0; 3691</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>424; 5940</t>
+          <t>453; 6794</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>844; 7330</t>
+          <t>860; 6697</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2978; 12543</t>
+          <t>2910; 13183</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1807; 10019</t>
+          <t>1745; 9938</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6192; 19210</t>
+          <t>6365; 19002</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5677; 18714</t>
+          <t>6170; 18666</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6712; 20753</t>
+          <t>6303; 19461</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14774; 32497</t>
+          <t>14634; 33181</t>
         </is>
       </c>
     </row>
